--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -1490,14 +1490,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1526,14 +1526,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1616,14 +1616,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -2216,22 +2216,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2242,16 +2234,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
       </c>
@@ -2290,7 +2278,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2384,18 +2372,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -2424,12 +2416,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F94" t="n">
         <v>3</v>
       </c>
@@ -2468,7 +2464,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2486,14 +2482,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -2504,12 +2508,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F98" t="n">
         <v>3</v>
       </c>
@@ -2540,22 +2548,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2996,14 +2996,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3140,14 +3140,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3648,18 +3648,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -3674,18 +3674,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -3700,22 +3700,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -3726,18 +3726,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -3748,18 +3752,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -3774,18 +3774,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -3800,22 +3800,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -744,22 +744,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -774,26 +770,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -804,26 +800,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -834,18 +826,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -860,18 +856,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1598,14 +1598,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1688,14 +1688,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1864,18 +1864,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1886,22 +1890,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2220,14 +2220,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2238,14 +2246,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2256,12 +2272,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F86" t="n">
         <v>3</v>
       </c>
@@ -2296,22 +2316,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -2340,22 +2352,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2384,16 +2388,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
         <v>3</v>
       </c>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2888,14 +2888,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -2996,14 +2996,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3360,14 +3360,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3496,22 +3496,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -3600,18 +3600,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -3652,18 +3648,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -3752,18 +3752,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -744,18 +744,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -770,26 +774,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -800,26 +804,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -830,22 +830,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.8%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -860,18 +856,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1864,22 +1864,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -1890,18 +1886,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3496,22 +3496,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -3752,18 +3752,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,22 +744,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -774,26 +774,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -804,18 +800,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -830,18 +826,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -856,26 +856,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1382,14 +1382,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1400,14 +1400,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1436,14 +1436,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1508,14 +1508,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1634,14 +1634,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1670,14 +1670,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1742,18 +1742,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -1768,18 +1768,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -1794,14 +1794,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -1816,14 +1816,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -1838,22 +1838,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -1864,18 +1860,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1886,18 +1886,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2194,14 +2194,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2212,18 +2220,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2234,18 +2246,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2256,14 +2272,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2274,7 +2298,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2292,7 +2316,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2310,7 +2334,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2328,22 +2352,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2354,14 +2370,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -2376,14 +2392,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -2398,7 +2414,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2416,7 +2432,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2434,7 +2450,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2452,7 +2468,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2470,22 +2486,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -2496,22 +2504,18 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -2522,12 +2526,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F99" t="n">
         <v>3</v>
       </c>
@@ -2540,22 +2548,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2798,14 +2798,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2906,14 +2906,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2942,14 +2942,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3032,14 +3032,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3360,14 +3360,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3382,14 +3382,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -3448,14 +3448,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -3496,18 +3496,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -3518,22 +3522,18 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -3570,18 +3570,18 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -3596,18 +3596,18 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -3622,22 +3622,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
@@ -3648,18 +3648,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -3700,18 +3700,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -3748,22 +3752,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -3774,18 +3778,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -3800,22 +3804,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -4150,18 +4150,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4190,7 +4186,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4208,14 +4204,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4262,14 +4262,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -4280,7 +4284,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4298,7 +4302,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4316,18 +4320,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -4338,14 +4338,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
@@ -4356,14 +4356,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -4392,14 +4392,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -4410,14 +4410,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4510,6 +4510,42 @@
         <v>3</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
